--- a/基本設定.xlsx
+++ b/基本設定.xlsx
@@ -541,12 +541,12 @@
   <sheetData>
     <row r="43" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A43" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A120" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.15">
